--- a/artfynd/A 54310-2025 artfynd.xlsx
+++ b/artfynd/A 54310-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>85527785</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509959.9327526857</v>
+        <v>509960</v>
       </c>
       <c r="R2" t="n">
-        <v>6751887.841616441</v>
+        <v>6751888</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2020-05-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-05-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>87787402</v>
       </c>
       <c r="B3" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509959.2737542451</v>
+        <v>509959</v>
       </c>
       <c r="R3" t="n">
-        <v>6751949.148843578</v>
+        <v>6751949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +852,9 @@
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
